--- a/artfynd/A 35160-2020 artfynd.xlsx
+++ b/artfynd/A 35160-2020 artfynd.xlsx
@@ -675,10 +675,10 @@
     </row>
     <row r="2">
       <c r="A2" t="n">
-        <v>123577626</v>
+        <v>123577378</v>
       </c>
       <c r="B2" t="n">
-        <v>78420</v>
+        <v>78426</v>
       </c>
       <c r="C2" t="inlineStr">
         <is>
@@ -715,13 +715,13 @@
         </is>
       </c>
       <c r="Q2" t="n">
-        <v>479989</v>
+        <v>479877</v>
       </c>
       <c r="R2" t="n">
-        <v>6864776</v>
+        <v>6864754</v>
       </c>
       <c r="S2" t="n">
-        <v>10</v>
+        <v>20</v>
       </c>
       <c r="T2" t="inlineStr">
         <is>
@@ -777,10 +777,10 @@
     </row>
     <row r="3">
       <c r="A3" t="n">
-        <v>123577378</v>
+        <v>123577626</v>
       </c>
       <c r="B3" t="n">
-        <v>78420</v>
+        <v>78426</v>
       </c>
       <c r="C3" t="inlineStr">
         <is>
@@ -817,13 +817,13 @@
         </is>
       </c>
       <c r="Q3" t="n">
-        <v>479877</v>
+        <v>479989</v>
       </c>
       <c r="R3" t="n">
-        <v>6864754</v>
+        <v>6864776</v>
       </c>
       <c r="S3" t="n">
-        <v>20</v>
+        <v>10</v>
       </c>
       <c r="T3" t="inlineStr">
         <is>
@@ -882,7 +882,7 @@
         <v>123577453</v>
       </c>
       <c r="B4" t="n">
-        <v>92247</v>
+        <v>92264</v>
       </c>
       <c r="C4" t="inlineStr">
         <is>
